--- a/OCT_2026/10-06-26/Gourmet Food 1.xlsx
+++ b/OCT_2026/10-06-26/Gourmet Food 1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7ADA4C-3044-4356-90AD-9DE82924FE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08F3969-F325-4A25-91DC-80378EA030DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="878" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="878" firstSheet="3" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -2757,7 +2757,7 @@
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="413">
+  <cellXfs count="414">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3939,6 +3939,9 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -48124,7 +48127,7 @@
       <c r="L4" s="369"/>
       <c r="M4" s="399">
         <f ca="1">TODAY()+1</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="N4" s="399"/>
       <c r="O4" s="399"/>
@@ -48152,7 +48155,7 @@
       <c r="L5" s="369"/>
       <c r="M5" s="399">
         <f ca="1">M4-1</f>
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="N5" s="368"/>
       <c r="O5" s="368"/>
@@ -55443,7 +55446,7 @@
       <c r="R21" s="299">
         <v>19</v>
       </c>
-      <c r="S21" s="317" t="str">
+      <c r="S21" s="413" t="str">
         <f>+'19'!A6:A6</f>
         <v>Gourmet Food Bata Pur</v>
       </c>
@@ -55626,7 +55629,7 @@
       <c r="R27" s="299">
         <v>25</v>
       </c>
-      <c r="S27" s="317" t="str">
+      <c r="S27" s="413" t="str">
         <f>+'25'!A6:A6</f>
         <v>Gourmet Food Shalimar Link Road</v>
       </c>
@@ -55639,7 +55642,7 @@
       <c r="R28" s="299">
         <v>26</v>
       </c>
-      <c r="S28" s="317" t="str">
+      <c r="S28" s="413" t="str">
         <f>+'26'!A6:A6</f>
         <v>Gourmet Food Salamat pura</v>
       </c>
